--- a/data-model-explorer/assets/Data_Model_Template.xlsx
+++ b/data-model-explorer/assets/Data_Model_Template.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table Dictionary'!$B$3:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Need (formus_Need)'!$A$11:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Need (formus_Need)'!$A$16:$N$17</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="33.6640625" customWidth="1" min="1" max="1"/>
@@ -943,6 +943,9 @@
     <col width="61" customWidth="1" min="9" max="9"/>
     <col width="39" customWidth="1" min="10" max="10"/>
     <col width="63" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.7" customHeight="1">
@@ -1018,122 +1021,187 @@
       <c r="B9" s="18" t="n"/>
     </row>
     <row r="10" ht="14.7" customHeight="1">
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>e.g. business logic or related automation</t>
-        </is>
-      </c>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Primary Name Column</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n"/>
     </row>
     <row r="11" ht="14.7" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
+          <t>Primary Key</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="14.7" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Is Activity</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="14.7" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Has Notes</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="14.7" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Has Activities</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="14.7" customHeight="1">
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>e.g. business logic or related automation</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>N:1 on a lookup row; N:N on a many-to-many row (Targets: other table in Additional data)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Optional: generated if blank</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Remove Link (default), Restrict or Cascade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14.7" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
           <t>Logical Name</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Schema Name</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Display Name</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Attribute Type</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>Custom Attribute</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Required Level</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>Additional data</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Add to RAF Form?</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="14.7" customHeight="1"/>
-    <row r="13" ht="14.7" customHeight="1"/>
-    <row r="14" ht="14.7" customHeight="1"/>
-    <row r="15" ht="14.7" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Forms:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="14.7" customHeight="1">
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Form Name</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Formus Comments</t>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Relationship Type</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>Relationship Name</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>Cascade Delete</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14.7" customHeight="1"/>
     <row r="18" ht="14.7" customHeight="1"/>
-    <row r="19" ht="14.7" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Views:</t>
-        </is>
-      </c>
-    </row>
+    <row r="19" ht="14.7" customHeight="1"/>
     <row r="20" ht="14.7" customHeight="1">
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>View Name</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Columns</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>Filter</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="14.7" customHeight="1"/>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Forms:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14.7" customHeight="1">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Form Name</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Formus Comments</t>
+        </is>
+      </c>
+    </row>
     <row r="22" ht="14.7" customHeight="1"/>
     <row r="23" ht="14.7" customHeight="1"/>
-    <row r="24" ht="14.7" customHeight="1"/>
-    <row r="25" ht="14.7" customHeight="1"/>
+    <row r="24" ht="14.7" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Views:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="14.7" customHeight="1">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>View Name</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Columns</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="14.7" customHeight="1"/>
     <row r="27" ht="14.7" customHeight="1"/>
     <row r="28" ht="14.7" customHeight="1"/>
@@ -1141,7 +1209,15 @@
     <row r="30" ht="216" customHeight="1"/>
     <row r="31" ht="14.7" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A11:K12"/>
+  <autoFilter ref="A16:N17"/>
+  <dataValidations count="2">
+    <dataValidation sqref="L17:L2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"N:1,N:N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N17:N2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Remove Link,Restrict,Cascade"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="9" min="0" max="16383" man="1"/>
